--- a/34th_Backgammon-championships_4d_output.xlsx
+++ b/34th_Backgammon-championships_4d_output.xlsx
@@ -1184,7 +1184,7 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
@@ -1254,7 +1254,7 @@
         <v>6</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
@@ -1312,7 +1312,7 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
         <v>5</v>
@@ -1345,7 +1345,7 @@
         <v>9</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
         <v>7</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="n">
         <v>9</v>
@@ -1550,7 +1550,7 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>5</v>
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>4</v>
